--- a/data/AHLdelegacije - kp narejena 16.12..xlsx
+++ b/data/AHLdelegacije - kp narejena 16.12..xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205BE38D-5A4D-4DB5-9B7E-BDC2782AA0C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FD6239-B905-466A-9D13-4124A5356F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHL" sheetId="1" r:id="rId1"/>
@@ -1438,7 +1438,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1545,6 +1545,8 @@
     <xf numFmtId="1" fontId="3" fillId="11" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1560,9 +1562,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2794,7 +2793,7 @@
       <c r="BH4" t="s">
         <v>80</v>
       </c>
-      <c r="BI4" s="65" t="s">
+      <c r="BI4" s="60" t="s">
         <v>76</v>
       </c>
       <c r="BJ4" t="s">
@@ -3001,7 +3000,6 @@
       <c r="BH5" t="s">
         <v>101</v>
       </c>
-      <c r="BI5" s="66"/>
       <c r="BJ5" t="s">
         <v>88</v>
       </c>
@@ -3221,7 +3219,7 @@
       <c r="BP6" t="s">
         <v>94</v>
       </c>
-      <c r="BQ6" s="65" t="s">
+      <c r="BQ6" s="60" t="s">
         <v>111</v>
       </c>
     </row>
@@ -3244,7 +3242,7 @@
       <c r="F7" t="s">
         <v>81</v>
       </c>
-      <c r="G7" s="65" t="s">
+      <c r="G7" s="60" t="s">
         <v>93</v>
       </c>
       <c r="H7" t="s">
@@ -3292,7 +3290,7 @@
       <c r="W7" t="s">
         <v>84</v>
       </c>
-      <c r="X7" s="65" t="s">
+      <c r="X7" s="60" t="s">
         <v>112</v>
       </c>
       <c r="Y7" t="s">
@@ -3397,7 +3395,7 @@
       <c r="BF7" t="s">
         <v>102</v>
       </c>
-      <c r="BG7" s="65" t="s">
+      <c r="BG7" s="60" t="s">
         <v>114</v>
       </c>
       <c r="BH7" s="8" t="s">
@@ -3441,7 +3439,6 @@
       <c r="F8" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="66"/>
       <c r="H8" t="s">
         <v>93</v>
       </c>
@@ -3583,7 +3580,7 @@
       <c r="BD8" t="s">
         <v>88</v>
       </c>
-      <c r="BE8" s="67" t="s">
+      <c r="BE8" s="61" t="s">
         <v>119</v>
       </c>
       <c r="BF8" t="s">
@@ -3705,7 +3702,7 @@
       <c r="AH9" t="s">
         <v>118</v>
       </c>
-      <c r="AI9" s="65" t="s">
+      <c r="AI9" s="60" t="s">
         <v>109</v>
       </c>
       <c r="AJ9" s="6" t="s">
@@ -3771,10 +3768,10 @@
       <c r="BD9" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="BF9" s="65" t="s">
+      <c r="BF9" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="BH9" s="65" t="s">
+      <c r="BH9" s="60" t="s">
         <v>112</v>
       </c>
       <c r="BJ9" t="s">
@@ -3789,10 +3786,10 @@
       <c r="BN9" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="BO9" s="65" t="s">
+      <c r="BO9" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="BP9" s="65" t="s">
+      <c r="BP9" s="60" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3953,8 +3950,7 @@
       <c r="BD10" t="s">
         <v>116</v>
       </c>
-      <c r="BF10" s="66"/>
-      <c r="BJ10" s="65" t="s">
+      <c r="BJ10" s="60" t="s">
         <v>104</v>
       </c>
       <c r="BK10" t="s">
@@ -3992,7 +3988,7 @@
       <c r="I11" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="J11" s="65" t="s">
+      <c r="J11" s="60" t="s">
         <v>124</v>
       </c>
       <c r="K11" t="s">
@@ -4195,7 +4191,7 @@
       <c r="W12" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="Y12" s="65" t="s">
+      <c r="Y12" s="60" t="s">
         <v>95</v>
       </c>
       <c r="Z12" t="s">
@@ -4225,7 +4221,7 @@
       <c r="AH12" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="AJ12" s="65" t="s">
+      <c r="AJ12" s="60" t="s">
         <v>92</v>
       </c>
       <c r="AK12" t="s">
@@ -4291,10 +4287,10 @@
       <c r="BK12" t="s">
         <v>121</v>
       </c>
-      <c r="BM12" s="65" t="s">
+      <c r="BM12" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="BN12" s="65" t="s">
+      <c r="BN12" s="60" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4314,7 +4310,7 @@
       <c r="E13" t="s">
         <v>106</v>
       </c>
-      <c r="F13" s="65" t="s">
+      <c r="F13" s="60" t="s">
         <v>121</v>
       </c>
       <c r="H13" t="s">
@@ -4374,7 +4370,7 @@
       <c r="AD13" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="AE13" s="65" t="s">
+      <c r="AE13" s="60" t="s">
         <v>119</v>
       </c>
       <c r="AF13" t="s">
@@ -4389,7 +4385,7 @@
       <c r="AK13" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="AL13" s="65" t="s">
+      <c r="AL13" s="60" t="s">
         <v>125</v>
       </c>
       <c r="AM13" t="s">
@@ -4410,13 +4406,13 @@
       <c r="AR13" t="s">
         <v>106</v>
       </c>
-      <c r="AS13" s="65" t="s">
+      <c r="AS13" s="60" t="s">
         <v>125</v>
       </c>
       <c r="AT13" t="s">
         <v>116</v>
       </c>
-      <c r="AU13" s="65" t="s">
+      <c r="AU13" s="60" t="s">
         <v>119</v>
       </c>
       <c r="AV13" t="s">
@@ -4440,13 +4436,13 @@
       <c r="BB13" t="s">
         <v>102</v>
       </c>
-      <c r="BC13" s="65" t="s">
+      <c r="BC13" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="BD13" s="65" t="s">
+      <c r="BD13" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="BK13" s="65" t="s">
+      <c r="BK13" s="60" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4454,10 +4450,10 @@
       <c r="A14" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="60" t="s">
         <v>124</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -4466,16 +4462,16 @@
       <c r="E14" t="s">
         <v>114</v>
       </c>
-      <c r="H14" s="65" t="s">
+      <c r="H14" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="65" t="s">
+      <c r="I14" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="K14" s="65" t="s">
+      <c r="K14" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="L14" s="65" t="s">
+      <c r="L14" s="60" t="s">
         <v>124</v>
       </c>
       <c r="N14" t="s">
@@ -4514,7 +4510,7 @@
       <c r="AA14" t="s">
         <v>111</v>
       </c>
-      <c r="AB14" s="65" t="s">
+      <c r="AB14" s="60" t="s">
         <v>92</v>
       </c>
       <c r="AC14" t="s">
@@ -4523,13 +4519,13 @@
       <c r="AD14" t="s">
         <v>112</v>
       </c>
-      <c r="AF14" s="65" t="s">
+      <c r="AF14" s="60" t="s">
         <v>111</v>
       </c>
       <c r="AG14" t="s">
         <v>125</v>
       </c>
-      <c r="AH14" s="65" t="s">
+      <c r="AH14" s="60" t="s">
         <v>125</v>
       </c>
       <c r="AK14" t="s">
@@ -4547,7 +4543,7 @@
       <c r="AP14" t="s">
         <v>121</v>
       </c>
-      <c r="AQ14" s="65" t="s">
+      <c r="AQ14" s="60" t="s">
         <v>124</v>
       </c>
       <c r="AR14" t="s">
@@ -4579,7 +4575,7 @@
       </c>
     </row>
     <row r="15" spans="1:69" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="65" t="s">
+      <c r="A15" s="60" t="s">
         <v>124</v>
       </c>
       <c r="D15" t="s">
@@ -4588,7 +4584,7 @@
       <c r="E15" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="N15" s="65" t="s">
+      <c r="N15" s="60" t="s">
         <v>125</v>
       </c>
       <c r="O15" t="s">
@@ -4612,7 +4608,7 @@
       <c r="U15" t="s">
         <v>100</v>
       </c>
-      <c r="V15" s="65" t="s">
+      <c r="V15" s="60" t="s">
         <v>124</v>
       </c>
       <c r="W15" t="s">
@@ -4627,10 +4623,10 @@
       <c r="AC15" t="s">
         <v>125</v>
       </c>
-      <c r="AD15" s="65" t="s">
+      <c r="AD15" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="AG15" s="65" t="s">
+      <c r="AG15" s="60" t="s">
         <v>117</v>
       </c>
       <c r="AK15" t="s">
@@ -4642,10 +4638,10 @@
       <c r="AN15" t="s">
         <v>128</v>
       </c>
-      <c r="AO15" s="65" t="s">
+      <c r="AO15" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="AP15" s="65" t="s">
+      <c r="AP15" s="60" t="s">
         <v>104</v>
       </c>
       <c r="AR15" s="7" t="s">
@@ -4654,7 +4650,7 @@
       <c r="AT15" t="s">
         <v>107</v>
       </c>
-      <c r="AV15" s="65" t="s">
+      <c r="AV15" s="60" t="s">
         <v>103</v>
       </c>
       <c r="AW15" t="s">
@@ -4683,7 +4679,7 @@
       <c r="E16" t="s">
         <v>103</v>
       </c>
-      <c r="O16" s="65" t="s">
+      <c r="O16" s="60" t="s">
         <v>121</v>
       </c>
       <c r="P16" t="s">
@@ -4698,7 +4694,7 @@
       <c r="S16" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="T16" s="65" t="s">
+      <c r="T16" s="60" t="s">
         <v>125</v>
       </c>
       <c r="U16" s="7" t="s">
@@ -4710,10 +4706,10 @@
       <c r="Z16" t="s">
         <v>111</v>
       </c>
-      <c r="AA16" s="65" t="s">
+      <c r="AA16" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="AC16" s="65" t="s">
+      <c r="AC16" s="60" t="s">
         <v>92</v>
       </c>
       <c r="AK16" t="s">
@@ -4722,7 +4718,7 @@
       <c r="AM16" t="s">
         <v>125</v>
       </c>
-      <c r="AN16" s="65" t="s">
+      <c r="AN16" s="60" t="s">
         <v>126</v>
       </c>
       <c r="AR16" t="s">
@@ -4737,7 +4733,7 @@
       <c r="AX16" t="s">
         <v>119</v>
       </c>
-      <c r="AY16" s="65" t="s">
+      <c r="AY16" s="60" t="s">
         <v>121</v>
       </c>
       <c r="AZ16" t="s">
@@ -4751,10 +4747,10 @@
       </c>
     </row>
     <row r="17" spans="4:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="65" t="s">
+      <c r="D17" s="60" t="s">
         <v>124</v>
       </c>
-      <c r="E17" s="65" t="s">
+      <c r="E17" s="60" t="s">
         <v>124</v>
       </c>
       <c r="P17" t="s">
@@ -4775,13 +4771,13 @@
       <c r="W17" t="s">
         <v>109</v>
       </c>
-      <c r="Z17" s="65" t="s">
+      <c r="Z17" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="AK17" s="65" t="s">
+      <c r="AK17" s="60" t="s">
         <v>125</v>
       </c>
-      <c r="AM17" s="65" t="s">
+      <c r="AM17" s="60" t="s">
         <v>121</v>
       </c>
       <c r="AR17" t="s">
@@ -4790,16 +4786,16 @@
       <c r="AT17" t="s">
         <v>111</v>
       </c>
-      <c r="AW17" s="65" t="s">
+      <c r="AW17" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="AX17" s="65" t="s">
+      <c r="AX17" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="AZ17" s="65" t="s">
+      <c r="AZ17" s="60" t="s">
         <v>121</v>
       </c>
-      <c r="BA17" s="65" t="s">
+      <c r="BA17" s="60" t="s">
         <v>127</v>
       </c>
       <c r="BB17" t="s">
@@ -4807,13 +4803,13 @@
       </c>
     </row>
     <row r="18" spans="4:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="P18" s="65" t="s">
+      <c r="P18" s="60" t="s">
         <v>119</v>
       </c>
       <c r="Q18" t="s">
         <v>111</v>
       </c>
-      <c r="R18" s="65" t="s">
+      <c r="R18" s="60" t="s">
         <v>111</v>
       </c>
       <c r="S18" t="s">
@@ -4822,7 +4818,7 @@
       <c r="U18" t="s">
         <v>112</v>
       </c>
-      <c r="W18" s="65" t="s">
+      <c r="W18" s="60" t="s">
         <v>111</v>
       </c>
       <c r="AR18" t="s">
@@ -4831,12 +4827,12 @@
       <c r="AT18" t="s">
         <v>119</v>
       </c>
-      <c r="BB18" s="65" t="s">
+      <c r="BB18" s="60" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="19" spans="4:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Q19" s="65" t="s">
+      <c r="Q19" s="60" t="s">
         <v>121</v>
       </c>
       <c r="S19" t="s">
@@ -4845,18 +4841,18 @@
       <c r="U19" t="s">
         <v>121</v>
       </c>
-      <c r="AR19" s="65" t="s">
+      <c r="AR19" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="AT19" s="65" t="s">
+      <c r="AT19" s="60" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="20" spans="4:54" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="S20" s="65" t="s">
+      <c r="S20" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="U20" s="65" t="s">
+      <c r="U20" s="60" t="s">
         <v>109</v>
       </c>
     </row>
@@ -8264,20 +8260,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="62" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="61"/>
+      <c r="B1" s="63"/>
       <c r="C1" s="9">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
         <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="64" t="s">
         <v>314</v>
       </c>
-      <c r="B2" s="63"/>
+      <c r="B2" s="65"/>
       <c r="C2" s="10">
         <f>C1*4</f>
         <v>736</v>
@@ -8291,12 +8287,12 @@
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>736</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="66" t="s">
         <v>315</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
@@ -8664,8 +8660,8 @@
       </c>
     </row>
     <row r="24" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
     </row>
     <row r="25" spans="5:17" ht="75.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
